--- a/database/diccionario datos-v2.xlsx
+++ b/database/diccionario datos-v2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6fd9368643786761/Documentación actual para corrección - copia/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eduar\Documents\trabajo isseg\SGSPCSI\Database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4CD0DC55-1632-4F58-898E-B5C4B745801D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F9A1B13-B2DE-46CA-B600-9BBD6465C4B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Historial de versiones" sheetId="34" r:id="rId1"/>
@@ -49,6 +49,9 @@
     <sheet name="evento_calendario" sheetId="32" r:id="rId34"/>
     <sheet name="evento_participante" sheetId="33" r:id="rId35"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">INDICE!$A$2:$D$35</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -67,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1711" uniqueCount="567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1701" uniqueCount="580">
   <si>
     <t>Descripción</t>
   </si>
@@ -1777,6 +1780,45 @@
   </si>
   <si>
     <t>Registra la asignación de usuarios a sistemas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">diccionario de datos </t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fecha y hora en que terminó la vigencia de la asignación. Si está vacía, la relación se considera vigente.	</t>
+  </si>
+  <si>
+    <t>tarea_desarrollo_asignacion_id</t>
+  </si>
+  <si>
+    <t>Identity</t>
+  </si>
+  <si>
+    <t>Identificador único de cada asignación. Se genera automáticamente por el sistema y permite distinguir de forma inequívoca cada relación entre una tarea y un usuario.</t>
+  </si>
+  <si>
+    <t>Identificador de la tarea de desarrollo a la que pertenece la asignación. Vincula el registro con la tarea operativa concreta que se está ejecutando.</t>
+  </si>
+  <si>
+    <t>Identificador del usuario asignado a la tarea. Permite saber qué persona participa en la ejecución del trabajo técnico.</t>
+  </si>
+  <si>
+    <t>rol_tecnico</t>
+  </si>
+  <si>
+    <t>Rol que desempeña el usuario dentro de la tarea. Define su función operativa, por ejemplo RESPONSABLE o PARTICIPANTE.</t>
+  </si>
+  <si>
+    <t>Indica si la asignación está vigente. Valor 1 significa que la persona sigue asignada; valor 0 significa que la asignación ya fue cerrada o desactivada.</t>
+  </si>
+  <si>
+    <t>Fecha y hora en que se creó la asignación. Sirve para trazabilidad, auditoría y control histórico de la participación del usuario en la tarea.</t>
+  </si>
+  <si>
+    <t>Fecha y hora en que terminó la asignación. Si está vacía, la relación sigue vigente. Permite conservar el historial de asignaciones cerradas.</t>
   </si>
 </sst>
 </file>
@@ -1855,7 +1897,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1980,12 +2022,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2059,6 +2110,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2079,9 +2137,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2389,12 +2444,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F3032A7-1FDA-4D94-AD06-8C9FD1BB5B90}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="4" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="36.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>342</v>
       </c>
@@ -2408,7 +2463,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2422,7 +2477,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>359</v>
       </c>
@@ -2436,7 +2491,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>361</v>
       </c>
@@ -2450,7 +2505,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>362</v>
       </c>
@@ -2464,7 +2519,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>363</v>
       </c>
@@ -2478,7 +2533,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>364</v>
       </c>
@@ -2492,7 +2547,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2</v>
       </c>
@@ -2506,7 +2561,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>365</v>
       </c>
@@ -2528,44 +2583,44 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
     <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" customWidth="1"/>
-    <col min="6" max="6" width="35.85546875" customWidth="1"/>
-    <col min="7" max="7" width="18.85546875" customWidth="1"/>
+    <col min="4" max="4" width="21.875" customWidth="1"/>
+    <col min="5" max="5" width="11.875" customWidth="1"/>
+    <col min="6" max="6" width="35.875" customWidth="1"/>
+    <col min="7" max="7" width="18.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-    </row>
-    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="41" t="s">
         <v>284</v>
       </c>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>67</v>
       </c>
@@ -2588,7 +2643,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>72</v>
       </c>
@@ -2609,7 +2664,7 @@
       </c>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>74</v>
       </c>
@@ -2628,7 +2683,7 @@
       </c>
       <c r="G5" s="4"/>
     </row>
-    <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
         <v>75</v>
@@ -2645,7 +2700,7 @@
       </c>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>103</v>
@@ -2676,44 +2731,44 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="1" max="1" width="24.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.875" customWidth="1"/>
     <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" customWidth="1"/>
-    <col min="6" max="6" width="35.85546875" customWidth="1"/>
-    <col min="7" max="7" width="25.85546875" customWidth="1"/>
+    <col min="4" max="4" width="21.875" customWidth="1"/>
+    <col min="5" max="5" width="11.875" customWidth="1"/>
+    <col min="6" max="6" width="35.875" customWidth="1"/>
+    <col min="7" max="7" width="25.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-    </row>
-    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="41" t="s">
         <v>287</v>
       </c>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>67</v>
       </c>
@@ -2736,7 +2791,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>72</v>
       </c>
@@ -2757,7 +2812,7 @@
       </c>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="4" t="s">
         <v>73</v>
@@ -2774,7 +2829,7 @@
       </c>
       <c r="G5" s="4"/>
     </row>
-    <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>74</v>
       </c>
@@ -2793,7 +2848,7 @@
       </c>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>119</v>
@@ -2810,7 +2865,7 @@
       </c>
       <c r="G7" s="4"/>
     </row>
-    <row r="8" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
         <v>103</v>
@@ -2841,44 +2896,44 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.85546875" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="1" max="1" width="31.875" customWidth="1"/>
+    <col min="2" max="2" width="21.875" customWidth="1"/>
     <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" customWidth="1"/>
-    <col min="6" max="6" width="56.7109375" customWidth="1"/>
-    <col min="7" max="7" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="21.875" customWidth="1"/>
+    <col min="5" max="5" width="11.875" customWidth="1"/>
+    <col min="6" max="6" width="56.75" customWidth="1"/>
+    <col min="7" max="7" width="25.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-    </row>
-    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="40" t="s">
         <v>282</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>67</v>
       </c>
@@ -2901,7 +2956,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>72</v>
       </c>
@@ -2922,7 +2977,7 @@
       </c>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>74</v>
       </c>
@@ -2941,7 +2996,7 @@
       </c>
       <c r="G5" s="4"/>
     </row>
-    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
         <v>75</v>
@@ -2958,7 +3013,7 @@
       </c>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>121</v>
@@ -2977,7 +3032,7 @@
       </c>
       <c r="G7" s="4"/>
     </row>
-    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
         <v>103</v>
@@ -3008,44 +3063,44 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:G18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="1" max="1" width="24.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.875" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" customWidth="1"/>
-    <col min="5" max="5" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="52.42578125" customWidth="1"/>
-    <col min="7" max="7" width="34.85546875" customWidth="1"/>
+    <col min="4" max="4" width="21.875" customWidth="1"/>
+    <col min="5" max="5" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="52.375" customWidth="1"/>
+    <col min="7" max="7" width="34.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="36" t="s">
         <v>296</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-    </row>
-    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="40" t="s">
         <v>318</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>67</v>
       </c>
@@ -3068,7 +3123,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>72</v>
       </c>
@@ -3089,7 +3144,7 @@
       </c>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>74</v>
       </c>
@@ -3108,7 +3163,7 @@
       </c>
       <c r="G5" s="4"/>
     </row>
-    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
         <v>125</v>
@@ -3125,7 +3180,7 @@
       </c>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>77</v>
@@ -3142,7 +3197,7 @@
       </c>
       <c r="G7" s="4"/>
     </row>
-    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>94</v>
       </c>
@@ -3163,7 +3218,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>94</v>
       </c>
@@ -3184,7 +3239,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>94</v>
       </c>
@@ -3205,7 +3260,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>94</v>
       </c>
@@ -3226,7 +3281,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>94</v>
       </c>
@@ -3247,7 +3302,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>94</v>
       </c>
@@ -3268,7 +3323,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="4"/>
       <c r="B14" s="4" t="s">
         <v>300</v>
@@ -3287,7 +3342,7 @@
       </c>
       <c r="G14" s="4"/>
     </row>
-    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="4"/>
       <c r="B15" s="4" t="s">
         <v>200</v>
@@ -3304,7 +3359,7 @@
       </c>
       <c r="G15" s="4"/>
     </row>
-    <row r="16" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" s="4"/>
       <c r="B16" s="4" t="s">
         <v>301</v>
@@ -3321,7 +3376,7 @@
       </c>
       <c r="G16" s="4"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="4"/>
       <c r="B17" s="4" t="s">
         <v>302</v>
@@ -3338,7 +3393,7 @@
       </c>
       <c r="G17" s="4"/>
     </row>
-    <row r="18" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A18" s="4"/>
       <c r="B18" s="4" t="s">
         <v>79</v>
@@ -3370,44 +3425,44 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:G10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="1" max="1" width="24.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.875" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" customWidth="1"/>
-    <col min="5" max="5" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="66.42578125" customWidth="1"/>
-    <col min="7" max="7" width="29.140625" customWidth="1"/>
+    <col min="4" max="4" width="21.875" customWidth="1"/>
+    <col min="5" max="5" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="66.375" customWidth="1"/>
+    <col min="7" max="7" width="29.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-    </row>
-    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="40" t="s">
         <v>335</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>67</v>
       </c>
@@ -3430,7 +3485,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>72</v>
       </c>
@@ -3451,7 +3506,7 @@
       </c>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>94</v>
       </c>
@@ -3472,7 +3527,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>94</v>
       </c>
@@ -3493,7 +3548,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
       <c r="B7" s="9" t="s">
         <v>336</v>
@@ -3510,7 +3565,7 @@
       </c>
       <c r="G7" s="4"/>
     </row>
-    <row r="8" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A8" s="9"/>
       <c r="B8" s="9" t="s">
         <v>79</v>
@@ -3529,7 +3584,7 @@
       </c>
       <c r="G8" s="4"/>
     </row>
-    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="9"/>
       <c r="B9" s="9" t="s">
         <v>97</v>
@@ -3548,7 +3603,7 @@
       </c>
       <c r="G9" s="4"/>
     </row>
-    <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="9"/>
       <c r="B10" s="9" t="s">
         <v>202</v>
@@ -3577,44 +3632,44 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:G10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.85546875" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="1" max="1" width="31.875" customWidth="1"/>
+    <col min="2" max="2" width="21.875" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" customWidth="1"/>
-    <col min="5" max="5" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="92.42578125" customWidth="1"/>
-    <col min="7" max="7" width="35.140625" customWidth="1"/>
+    <col min="4" max="4" width="21.875" customWidth="1"/>
+    <col min="5" max="5" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="92.375" customWidth="1"/>
+    <col min="7" max="7" width="35.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="36" t="s">
         <v>552</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-    </row>
-    <row r="2" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+    </row>
+    <row r="2" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="41" t="s">
         <v>548</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>67</v>
       </c>
@@ -3637,7 +3692,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
         <v>72</v>
       </c>
@@ -3658,7 +3713,7 @@
       </c>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
         <v>94</v>
       </c>
@@ -3679,7 +3734,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
         <v>94</v>
       </c>
@@ -3700,7 +3755,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
         <v>94</v>
       </c>
@@ -3721,7 +3776,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
       <c r="A8" s="15"/>
       <c r="B8" s="15" t="s">
         <v>134</v>
@@ -3738,7 +3793,7 @@
       </c>
       <c r="G8" s="15"/>
     </row>
-    <row r="9" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
         <v>94</v>
       </c>
@@ -3759,7 +3814,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
       <c r="A10" s="15"/>
       <c r="B10" s="15" t="s">
         <v>136</v>
@@ -3790,44 +3845,44 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:G9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="1" max="1" width="24.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.875" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" customWidth="1"/>
-    <col min="5" max="5" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.85546875" customWidth="1"/>
-    <col min="7" max="7" width="36.140625" customWidth="1"/>
+    <col min="4" max="4" width="21.875" customWidth="1"/>
+    <col min="5" max="5" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.875" customWidth="1"/>
+    <col min="7" max="7" width="36.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="36" t="s">
         <v>553</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-    </row>
-    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="40" t="s">
         <v>378</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
         <v>67</v>
       </c>
@@ -3850,7 +3905,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>72</v>
       </c>
@@ -3871,7 +3926,7 @@
       </c>
       <c r="G4" s="9"/>
     </row>
-    <row r="5" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>94</v>
       </c>
@@ -3892,7 +3947,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>94</v>
       </c>
@@ -3913,7 +3968,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
       <c r="B7" s="9" t="s">
         <v>371</v>
@@ -3930,7 +3985,7 @@
       </c>
       <c r="G7" s="9"/>
     </row>
-    <row r="8" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
       <c r="A8" s="9"/>
       <c r="B8" s="9" t="s">
         <v>373</v>
@@ -3947,7 +4002,7 @@
       </c>
       <c r="G8" s="9"/>
     </row>
-    <row r="9" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
       <c r="A9" s="9"/>
       <c r="B9" s="9" t="s">
         <v>375</v>
@@ -3978,44 +4033,44 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:G9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="1" max="1" width="24.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.875" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" customWidth="1"/>
-    <col min="5" max="5" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.875" customWidth="1"/>
+    <col min="5" max="5" width="17.625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="54" customWidth="1"/>
-    <col min="7" max="7" width="26.140625" customWidth="1"/>
+    <col min="7" max="7" width="26.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="36" t="s">
         <v>554</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-    </row>
-    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="40" t="s">
         <v>380</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>67</v>
       </c>
@@ -4038,7 +4093,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>72</v>
       </c>
@@ -4059,7 +4114,7 @@
       </c>
       <c r="G4" s="13"/>
     </row>
-    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>94</v>
       </c>
@@ -4080,7 +4135,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
         <v>94</v>
       </c>
@@ -4101,7 +4156,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="13"/>
       <c r="B7" s="13" t="s">
         <v>134</v>
@@ -4118,7 +4173,7 @@
       </c>
       <c r="G7" s="13"/>
     </row>
-    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="13"/>
       <c r="B8" s="13" t="s">
         <v>388</v>
@@ -4137,7 +4192,7 @@
       </c>
       <c r="G8" s="13"/>
     </row>
-    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="13"/>
       <c r="B9" s="13" t="s">
         <v>139</v>
@@ -4168,44 +4223,44 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.85546875" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="1" max="1" width="31.875" customWidth="1"/>
+    <col min="2" max="2" width="21.875" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" customWidth="1"/>
-    <col min="5" max="5" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="64.5703125" customWidth="1"/>
-    <col min="7" max="7" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.875" customWidth="1"/>
+    <col min="5" max="5" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="64.625" customWidth="1"/>
+    <col min="7" max="7" width="17.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="36" t="s">
         <v>555</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-    </row>
-    <row r="2" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+    </row>
+    <row r="2" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="41" t="s">
         <v>395</v>
       </c>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>67</v>
       </c>
@@ -4228,7 +4283,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>72</v>
       </c>
@@ -4249,7 +4304,7 @@
       </c>
       <c r="G4" s="10"/>
     </row>
-    <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>94</v>
       </c>
@@ -4270,7 +4325,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="10"/>
       <c r="B6" s="10" t="s">
         <v>140</v>
@@ -4287,7 +4342,7 @@
       </c>
       <c r="G6" s="10"/>
     </row>
-    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="10"/>
       <c r="B7" s="10" t="s">
         <v>141</v>
@@ -4304,7 +4359,7 @@
       </c>
       <c r="G7" s="10"/>
     </row>
-    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="10"/>
       <c r="B8" s="10" t="s">
         <v>401</v>
@@ -4321,7 +4376,7 @@
       </c>
       <c r="G8" s="10"/>
     </row>
-    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="10"/>
       <c r="B9" s="10" t="s">
         <v>143</v>
@@ -4340,7 +4395,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
         <v>94</v>
       </c>
@@ -4359,7 +4414,7 @@
       </c>
       <c r="G10" s="10"/>
     </row>
-    <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="10"/>
       <c r="B11" s="10" t="s">
         <v>145</v>
@@ -4378,7 +4433,7 @@
       </c>
       <c r="G11" s="10"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -4387,7 +4442,7 @@
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -4395,7 +4450,7 @@
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -4403,7 +4458,7 @@
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -4411,7 +4466,7 @@
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -4419,7 +4474,7 @@
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -4427,7 +4482,7 @@
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -4435,7 +4490,7 @@
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -4443,7 +4498,7 @@
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -4463,44 +4518,44 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="1" max="1" width="24.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.875" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" customWidth="1"/>
-    <col min="5" max="5" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="69.5703125" customWidth="1"/>
-    <col min="7" max="7" width="26.7109375" customWidth="1"/>
+    <col min="4" max="4" width="21.875" customWidth="1"/>
+    <col min="5" max="5" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="69.625" customWidth="1"/>
+    <col min="7" max="7" width="26.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="36" t="s">
         <v>304</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-    </row>
-    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="40" t="s">
         <v>406</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>67</v>
       </c>
@@ -4523,7 +4578,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>72</v>
       </c>
@@ -4544,7 +4599,7 @@
       </c>
       <c r="G4" s="7"/>
     </row>
-    <row r="5" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>94</v>
       </c>
@@ -4565,7 +4620,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>94</v>
       </c>
@@ -4586,7 +4641,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="7" t="s">
         <v>125</v>
@@ -4603,7 +4658,7 @@
       </c>
       <c r="G7" s="7"/>
     </row>
-    <row r="8" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
       <c r="B8" s="7" t="s">
         <v>147</v>
@@ -4620,7 +4675,7 @@
       </c>
       <c r="G8" s="7"/>
     </row>
-    <row r="9" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
       <c r="B9" s="7" t="s">
         <v>148</v>
@@ -4639,7 +4694,7 @@
       </c>
       <c r="G9" s="7"/>
     </row>
-    <row r="10" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
       <c r="B10" s="9" t="s">
         <v>81</v>
@@ -4658,7 +4713,7 @@
       </c>
       <c r="G10" s="7"/>
     </row>
-    <row r="11" spans="1:7" ht="33" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="33.6" x14ac:dyDescent="0.3">
       <c r="A11" s="7"/>
       <c r="B11" s="9" t="s">
         <v>415</v>
@@ -4686,19 +4741,34 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:I35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J43"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="34.85546875" customWidth="1"/>
-    <col min="2" max="2" width="64.85546875" customWidth="1"/>
-    <col min="3" max="3" width="11.85546875" customWidth="1"/>
-    <col min="4" max="4" width="34.85546875" customWidth="1"/>
-    <col min="8" max="9" width="9" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" customWidth="1"/>
+    <col min="1" max="1" width="34.875" customWidth="1"/>
+    <col min="2" max="2" width="64.875" customWidth="1"/>
+    <col min="3" max="3" width="11.875" customWidth="1"/>
+    <col min="4" max="4" width="34.875" customWidth="1"/>
+    <col min="5" max="5" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9" customWidth="1"/>
+    <col min="10" max="10" width="8.875" customWidth="1"/>
     <col min="11" max="11" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="35" t="s">
+        <v>567</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+    </row>
+    <row r="2" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>322</v>
       </c>
@@ -4712,536 +4782,556 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="13">
+        <f t="shared" ref="C3:C35" ca="1" si="0">IFERROR(COUNTA(INDIRECT("'"&amp;D3&amp;"'!B4:B55")),0)</f>
+        <v>10</v>
+      </c>
+      <c r="D3" s="32" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="D4" s="32" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="D5" s="32" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="D6" s="32" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="D8" s="32" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="D9" s="32" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="D10" s="32" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="D11" s="32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="D12" s="32" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="D13" s="32" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="D14" s="32" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="D15" s="32" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B16" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="13">
-        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D3&amp;"'!B4:B55")),0)</f>
+      <c r="C16" s="13">
+        <f t="shared" ca="1" si="0"/>
         <v>6</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="D16" s="32" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="D17" s="32" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="D18" s="32" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15" x14ac:dyDescent="0.3">
+      <c r="A19" s="13" t="s">
+        <v>551</v>
+      </c>
+      <c r="B19" s="33" t="s">
+        <v>566</v>
+      </c>
+      <c r="C19" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="D19" s="32" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="D20" s="32" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="13" t="s">
+        <v>555</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="D21" s="32" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="13" t="s">
+        <v>553</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="D22" s="32" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="13" t="s">
+        <v>554</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="D23" s="32" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="D24" s="32" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="13" t="s">
+        <v>552</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="D25" s="32" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="D26" s="32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="D27" s="32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="D28" s="32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C29" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="D29" s="32" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="D30" s="32" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="D31" s="32" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B32" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="13">
-        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D4&amp;"'!B4:B55")),0)</f>
+      <c r="C32" s="13">
+        <f t="shared" ca="1" si="0"/>
         <v>8</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D32" s="32" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" s="13">
+        <f t="shared" ca="1" si="0"/>
         <v>7</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="D33" s="32" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="D34" s="32" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="13">
-        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D5&amp;"'!B4:B55")),0)</f>
-        <v>5</v>
-      </c>
-      <c r="D5" s="32" t="s">
+      <c r="C35" s="13">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="D35" s="32" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="13">
-        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D6&amp;"'!B4:B55")),0)</f>
-        <v>8</v>
-      </c>
-      <c r="D6" s="32" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="13">
-        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D7&amp;"'!B4:B55")),0)</f>
-        <v>7</v>
-      </c>
-      <c r="D7" s="32" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="13">
-        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D8&amp;"'!B4:B55")),0)</f>
-        <v>6</v>
-      </c>
-      <c r="D8" s="32" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="13">
-        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D9&amp;"'!B4:B55")),0)</f>
-        <v>5</v>
-      </c>
-      <c r="D9" s="32" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="13">
-        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D10&amp;"'!B4:B55")),0)</f>
-        <v>4</v>
-      </c>
-      <c r="D10" s="32" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="13">
-        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D11&amp;"'!B4:B55")),0)</f>
-        <v>5</v>
-      </c>
-      <c r="D11" s="32" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="13">
-        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D12&amp;"'!B4:B55")),0)</f>
-        <v>5</v>
-      </c>
-      <c r="D12" s="32" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="13">
-        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D13&amp;"'!B4:B55")),0)</f>
-        <v>15</v>
-      </c>
-      <c r="D13" s="32" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="13">
-        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D14&amp;"'!B4:B55")),0)</f>
-        <v>7</v>
-      </c>
-      <c r="D14" s="32" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
-        <v>552</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="13">
-        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D15&amp;"'!B4:B55")),0)</f>
-        <v>7</v>
-      </c>
-      <c r="D15" s="32" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="13" t="s">
-        <v>553</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" s="13">
-        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D16&amp;"'!B4:B55")),0)</f>
-        <v>6</v>
-      </c>
-      <c r="D16" s="32" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="13" t="s">
-        <v>554</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" s="13">
-        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D17&amp;"'!B4:B55")),0)</f>
-        <v>6</v>
-      </c>
-      <c r="D17" s="32" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="13" t="s">
-        <v>555</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C18" s="13">
-        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D18&amp;"'!B4:B55")),0)</f>
-        <v>8</v>
-      </c>
-      <c r="D18" s="32" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C19" s="13">
-        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D19&amp;"'!B4:B55")),0)</f>
-        <v>8</v>
-      </c>
-      <c r="D19" s="32" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C20" s="13">
-        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D20&amp;"'!B4:B55")),0)</f>
-        <v>11</v>
-      </c>
-      <c r="D20" s="32" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" s="13">
-        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D21&amp;"'!B4:B55")),0)</f>
-        <v>8</v>
-      </c>
-      <c r="D21" s="32" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" s="13">
-        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D22&amp;"'!B4:B55")),0)</f>
-        <v>6</v>
-      </c>
-      <c r="D22" s="32" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" s="13">
-        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D23&amp;"'!B4:B55")),0)</f>
-        <v>4</v>
-      </c>
-      <c r="D23" s="32" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" s="13">
-        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D24&amp;"'!B4:B55")),0)</f>
-        <v>8</v>
-      </c>
-      <c r="D24" s="32" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="C25" s="13">
-        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D25&amp;"'!B4:B55")),0)</f>
-        <v>11</v>
-      </c>
-      <c r="D25" s="32" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="C26" s="13">
-        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D26&amp;"'!B4:B55")),0)</f>
-        <v>11</v>
-      </c>
-      <c r="D26" s="32" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="B27" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="C27" s="13">
-        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D27&amp;"'!B4:B55")),0)</f>
-        <v>11</v>
-      </c>
-      <c r="D27" s="32" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="B28" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="C28" s="13">
-        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D28&amp;"'!B4:B55")),0)</f>
-        <v>10</v>
-      </c>
-      <c r="D28" s="32" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="B29" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="C29" s="13">
-        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D29&amp;"'!B4:B55")),0)</f>
-        <v>10</v>
-      </c>
-      <c r="D29" s="32" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="B30" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="C30" s="13">
-        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D30&amp;"'!B4:B55")),0)</f>
-        <v>4</v>
-      </c>
-      <c r="D30" s="32" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="B31" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C31" s="13">
-        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D31&amp;"'!B4:B55")),0)</f>
-        <v>8</v>
-      </c>
-      <c r="D31" s="32" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="13" t="s">
-        <v>551</v>
-      </c>
-      <c r="B32" s="40" t="s">
-        <v>566</v>
-      </c>
-      <c r="C32" s="13">
-        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D32&amp;"'!B4:B55")),0)</f>
-        <v>7</v>
-      </c>
-      <c r="D32" s="32" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="B33" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="C33" s="13">
-        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D33&amp;"'!B4:B55")),0)</f>
-        <v>11</v>
-      </c>
-      <c r="D33" s="32" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="B34" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="C34" s="13">
-        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D34&amp;"'!B4:B55")),0)</f>
-        <v>10</v>
-      </c>
-      <c r="D34" s="32" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="B35" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="C35" s="13">
-        <f ca="1">IFERROR(COUNTA(INDIRECT("'"&amp;D35&amp;"'!B4:B55")),0)</f>
-        <v>4</v>
-      </c>
-      <c r="D35" s="32" t="s">
-        <v>61</v>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C37">
+        <f ca="1">SUM(C3:C35)</f>
+        <v>247</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F43" t="s">
+        <v>568</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A2:D35" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D35">
+      <sortCondition ref="A2:A35"/>
+    </sortState>
+  </autoFilter>
+  <mergeCells count="2">
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D3" location="rol!A1" display="rol" xr:uid="{2B4614B3-B5C2-49A8-B649-B3B7A56F5F1E}"/>
-    <hyperlink ref="D4" location="usuario!A1" display="usuario" xr:uid="{EF6474E4-B295-4286-91B1-AD4657BD0CAD}"/>
-    <hyperlink ref="D5" location="usuario_rol!A1" display="usuario_rol" xr:uid="{5CADD67B-ADEE-4809-9265-387EC8F2DA1E}"/>
-    <hyperlink ref="D6" location="area!A1" display="area" xr:uid="{13DEA009-702D-4051-B272-D43DBD7A71D4}"/>
-    <hyperlink ref="D7" location="usuario_area!A1" display="usuario_area" xr:uid="{0F1E2726-E2B5-416A-B405-257D796E22CC}"/>
-    <hyperlink ref="D8" location="sistema!A1" display="sistema" xr:uid="{ADAA6A1D-4B15-4E60-9776-FCF2FC3DFD1C}"/>
-    <hyperlink ref="D9" location="area_sistema!A1" display="area_sistema" xr:uid="{795CB534-5703-4B70-B2D0-8B0E6AE13037}"/>
-    <hyperlink ref="D10" location="tipo_solicitud!A1" display="tipo_solicitud" xr:uid="{B2DB8C43-5E3D-488B-B173-D3EB88D51C09}"/>
-    <hyperlink ref="D11" location="prioridad_solicitud!A1" display="prioridad_solicitud" xr:uid="{3FA2CEDC-2839-41D0-A495-D9919BC6EBF7}"/>
-    <hyperlink ref="D12" location="estado_solicitud!A1" display="estado_solicitud" xr:uid="{1F073571-531A-4F1B-A954-5DDF15E6A1C9}"/>
-    <hyperlink ref="D13" location="solicitud!A1" display="solicitud" xr:uid="{632C16CC-3B6E-48E3-8D34-6C8DDE3803B4}"/>
-    <hyperlink ref="D14" location="'solicitud_desarrollador'!A1" display="solicitud_desarrollador" xr:uid="{74970300-8BD4-42BA-BF7C-880FC2F65753}"/>
-    <hyperlink ref="D15" location="solicitud_historial_estado!A1" display="solicitud_historial_estado" xr:uid="{242F7E10-6D13-44A7-8FA4-026C89728791}"/>
-    <hyperlink ref="D16" location="solicitud_aprobacion!A1" display="solicitud_aprobacion" xr:uid="{B093588F-7E4E-43D4-93F8-21380A0EF26D}"/>
-    <hyperlink ref="D17" location="solicitud_comentario!A1" display="solicitud_comentario" xr:uid="{D2F3E127-2BAF-49DD-9250-B1B182FB42BF}"/>
-    <hyperlink ref="D18" location="solicitud_adjunto!A1" display="solicitud_adjunto" xr:uid="{C256EC25-1819-4E94-A290-CE63736A8BBB}"/>
-    <hyperlink ref="D19" location="notificacion!A1" display="notificacion" xr:uid="{0A5FDBCB-4F45-4BFA-809C-5C86F9F68072}"/>
-    <hyperlink ref="D20" location="usuario_credencial!A1" display="usuario_credencial" xr:uid="{6DCD632A-A57E-498E-8C09-B502DF634D2D}"/>
-    <hyperlink ref="D21" location="menu_opcion!A1" display="menu_opcion" xr:uid="{4487E834-90EB-4CB1-BA2B-EF51886DFA66}"/>
-    <hyperlink ref="D22" location="rol_menu_opcion!A1" display="rol_menu_opcion" xr:uid="{DB31B0C5-ABD0-427E-ADAD-A59CF79CA713}"/>
-    <hyperlink ref="D23" location="tipo_modificacion!A1" display="tipo_modificacion" xr:uid="{2318DC5E-151D-4539-9F62-B7877DC48FA4}"/>
-    <hyperlink ref="D24" location="solicitud_modificacion!A1" display="solicitud_modificacion" xr:uid="{C47F83B0-D9FF-4067-8A85-DC81084EE9F4}"/>
-    <hyperlink ref="D25" location="solicitud_requerimiento_tecnico!A1" display="solicitud_requerimiento_tecnico" xr:uid="{026C352A-D6A5-4212-BCFB-557505736F5C}"/>
-    <hyperlink ref="D26" location="tarea_desarrollo!A1" display="tarea_desarrollo" xr:uid="{E9BD436A-F838-4EEA-9476-0D70FAB6C8A7}"/>
-    <hyperlink ref="D27" location="tarea_desarrollo_asignacion!A1" display="tarea_desarrollo_asignacion" xr:uid="{02665E46-86D7-45DC-B388-4A7F2A38E402}"/>
-    <hyperlink ref="D28" location="actividad_reciente!A1" display="actividad_reciente" xr:uid="{A28BE65C-2567-4017-9291-86D89FCD485D}"/>
-    <hyperlink ref="D29" location="proyecto!A1" display="proyecto" xr:uid="{0215288B-2E91-4CFB-B049-6FE438EEDBCF}"/>
-    <hyperlink ref="D30" location="proyecto_solicitud!A1" display="proyecto_solicitud" xr:uid="{7006D0C4-1325-443E-921A-51685992685F}"/>
-    <hyperlink ref="D31" location="proyecto_miembro!A1" display="proyecto_miembro" xr:uid="{A80B0950-37B5-4D7E-9B42-696F6382A1F2}"/>
-    <hyperlink ref="D33" location="documento_proyecto!A1" display="documento_proyecto" xr:uid="{0808F433-6682-4B84-95C8-51AC0C062DD1}"/>
-    <hyperlink ref="D35" location="evento_participante!A1" display="evento_participante" xr:uid="{70A16F5F-9B82-4A64-9262-91F18251F6DC}"/>
-    <hyperlink ref="D34" location="evento_calendario!A1" display="evento_calendario" xr:uid="{DFC53FFB-E375-46CF-9532-85DA4ADF49D7}"/>
-    <hyperlink ref="D32" location="sistema_desarrollador!A1" display="sistema_desarrollador" xr:uid="{DAB7F0B9-F482-4DA8-868D-D78D6B0583BF}"/>
+    <hyperlink ref="D16" location="rol!A1" display="rol" xr:uid="{2B4614B3-B5C2-49A8-B649-B3B7A56F5F1E}"/>
+    <hyperlink ref="D32" location="usuario!A1" display="usuario" xr:uid="{EF6474E4-B295-4286-91B1-AD4657BD0CAD}"/>
+    <hyperlink ref="D35" location="usuario_rol!A1" display="usuario_rol" xr:uid="{5CADD67B-ADEE-4809-9265-387EC8F2DA1E}"/>
+    <hyperlink ref="D4" location="area!A1" display="area" xr:uid="{13DEA009-702D-4051-B272-D43DBD7A71D4}"/>
+    <hyperlink ref="D33" location="usuario_area!A1" display="usuario_area" xr:uid="{0F1E2726-E2B5-416A-B405-257D796E22CC}"/>
+    <hyperlink ref="D18" location="sistema!A1" display="sistema" xr:uid="{ADAA6A1D-4B15-4E60-9776-FCF2FC3DFD1C}"/>
+    <hyperlink ref="D5" location="area_sistema!A1" display="area_sistema" xr:uid="{795CB534-5703-4B70-B2D0-8B0E6AE13037}"/>
+    <hyperlink ref="D31" location="tipo_solicitud!A1" display="tipo_solicitud" xr:uid="{B2DB8C43-5E3D-488B-B173-D3EB88D51C09}"/>
+    <hyperlink ref="D12" location="prioridad_solicitud!A1" display="prioridad_solicitud" xr:uid="{3FA2CEDC-2839-41D0-A495-D9919BC6EBF7}"/>
+    <hyperlink ref="D7" location="estado_solicitud!A1" display="estado_solicitud" xr:uid="{1F073571-531A-4F1B-A954-5DDF15E6A1C9}"/>
+    <hyperlink ref="D20" location="solicitud!A1" display="solicitud" xr:uid="{632C16CC-3B6E-48E3-8D34-6C8DDE3803B4}"/>
+    <hyperlink ref="D24" location="'solicitud_desarrollador'!A1" display="solicitud_desarrollador" xr:uid="{74970300-8BD4-42BA-BF7C-880FC2F65753}"/>
+    <hyperlink ref="D25" location="solicitud_historial_estado!A1" display="solicitud_historial_estado" xr:uid="{242F7E10-6D13-44A7-8FA4-026C89728791}"/>
+    <hyperlink ref="D22" location="solicitud_aprobacion!A1" display="solicitud_aprobacion" xr:uid="{B093588F-7E4E-43D4-93F8-21380A0EF26D}"/>
+    <hyperlink ref="D23" location="solicitud_comentario!A1" display="solicitud_comentario" xr:uid="{D2F3E127-2BAF-49DD-9250-B1B182FB42BF}"/>
+    <hyperlink ref="D21" location="solicitud_adjunto!A1" display="solicitud_adjunto" xr:uid="{C256EC25-1819-4E94-A290-CE63736A8BBB}"/>
+    <hyperlink ref="D11" location="notificacion!A1" display="notificacion" xr:uid="{0A5FDBCB-4F45-4BFA-809C-5C86F9F68072}"/>
+    <hyperlink ref="D34" location="usuario_credencial!A1" display="usuario_credencial" xr:uid="{6DCD632A-A57E-498E-8C09-B502DF634D2D}"/>
+    <hyperlink ref="D10" location="menu_opcion!A1" display="menu_opcion" xr:uid="{4487E834-90EB-4CB1-BA2B-EF51886DFA66}"/>
+    <hyperlink ref="D17" location="rol_menu_opcion!A1" display="rol_menu_opcion" xr:uid="{DB31B0C5-ABD0-427E-ADAD-A59CF79CA713}"/>
+    <hyperlink ref="D30" location="tipo_modificacion!A1" display="tipo_modificacion" xr:uid="{2318DC5E-151D-4539-9F62-B7877DC48FA4}"/>
+    <hyperlink ref="D26" location="solicitud_modificacion!A1" display="solicitud_modificacion" xr:uid="{C47F83B0-D9FF-4067-8A85-DC81084EE9F4}"/>
+    <hyperlink ref="D27" location="solicitud_requerimiento_tecnico!A1" display="solicitud_requerimiento_tecnico" xr:uid="{026C352A-D6A5-4212-BCFB-557505736F5C}"/>
+    <hyperlink ref="D28" location="tarea_desarrollo!A1" display="tarea_desarrollo" xr:uid="{E9BD436A-F838-4EEA-9476-0D70FAB6C8A7}"/>
+    <hyperlink ref="D29" location="tarea_desarrollo_asignacion!A1" display="tarea_desarrollo_asignacion" xr:uid="{02665E46-86D7-45DC-B388-4A7F2A38E402}"/>
+    <hyperlink ref="D3" location="actividad_reciente!A1" display="actividad_reciente" xr:uid="{A28BE65C-2567-4017-9291-86D89FCD485D}"/>
+    <hyperlink ref="D13" location="proyecto!A1" display="proyecto" xr:uid="{0215288B-2E91-4CFB-B049-6FE438EEDBCF}"/>
+    <hyperlink ref="D15" location="proyecto_solicitud!A1" display="proyecto_solicitud" xr:uid="{7006D0C4-1325-443E-921A-51685992685F}"/>
+    <hyperlink ref="D14" location="proyecto_miembro!A1" display="proyecto_miembro" xr:uid="{A80B0950-37B5-4D7E-9B42-696F6382A1F2}"/>
+    <hyperlink ref="D6" location="documento_proyecto!A1" display="documento_proyecto" xr:uid="{0808F433-6682-4B84-95C8-51AC0C062DD1}"/>
+    <hyperlink ref="D9" location="evento_participante!A1" display="evento_participante" xr:uid="{70A16F5F-9B82-4A64-9262-91F18251F6DC}"/>
+    <hyperlink ref="D8" location="evento_calendario!A1" display="evento_calendario" xr:uid="{DFC53FFB-E375-46CF-9532-85DA4ADF49D7}"/>
+    <hyperlink ref="D19" location="sistema_desarrollador!A1" display="sistema_desarrollador" xr:uid="{DAB7F0B9-F482-4DA8-868D-D78D6B0583BF}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -5251,45 +5341,45 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" customWidth="1"/>
-    <col min="5" max="5" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="58.28515625" customWidth="1"/>
-    <col min="7" max="7" width="26.140625" customWidth="1"/>
-    <col min="8" max="8" width="41.140625" customWidth="1"/>
+    <col min="1" max="1" width="24.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.875" customWidth="1"/>
+    <col min="5" max="5" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="58.25" customWidth="1"/>
+    <col min="7" max="7" width="26.125" customWidth="1"/>
+    <col min="8" max="8" width="41.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="36" t="s">
         <v>305</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-    </row>
-    <row r="2" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+    </row>
+    <row r="2" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="42" t="s">
         <v>417</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>67</v>
       </c>
@@ -5312,7 +5402,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="26" t="s">
         <v>162</v>
       </c>
@@ -5333,7 +5423,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>74</v>
       </c>
@@ -5352,7 +5442,7 @@
       </c>
       <c r="G5" s="4"/>
     </row>
-    <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
         <v>150</v>
@@ -5369,7 +5459,7 @@
       </c>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>152</v>
@@ -5386,7 +5476,7 @@
       </c>
       <c r="G7" s="4"/>
     </row>
-    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
         <v>154</v>
@@ -5405,7 +5495,7 @@
       </c>
       <c r="G8" s="4"/>
     </row>
-    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
         <v>155</v>
@@ -5424,7 +5514,7 @@
       </c>
       <c r="G9" s="4"/>
     </row>
-    <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
         <v>156</v>
@@ -5441,7 +5531,7 @@
       </c>
       <c r="G10" s="4"/>
     </row>
-    <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
         <v>157</v>
@@ -5460,7 +5550,7 @@
       </c>
       <c r="G11" s="4"/>
     </row>
-    <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
       <c r="B12" s="4" t="s">
         <v>159</v>
@@ -5477,7 +5567,7 @@
       </c>
       <c r="G12" s="4"/>
     </row>
-    <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="4"/>
       <c r="B13" s="4" t="s">
         <v>160</v>
@@ -5496,7 +5586,7 @@
       </c>
       <c r="G13" s="4"/>
     </row>
-    <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="4"/>
       <c r="B14" s="4" t="s">
         <v>161</v>
@@ -5527,44 +5617,44 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="1" max="1" width="24.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.875" customWidth="1"/>
     <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" customWidth="1"/>
-    <col min="6" max="6" width="66.28515625" customWidth="1"/>
-    <col min="7" max="7" width="19.85546875" customWidth="1"/>
+    <col min="4" max="4" width="21.875" customWidth="1"/>
+    <col min="5" max="5" width="11.875" customWidth="1"/>
+    <col min="6" max="6" width="66.25" customWidth="1"/>
+    <col min="7" max="7" width="19.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="36" t="s">
         <v>306</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-    </row>
-    <row r="2" spans="1:7" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+    </row>
+    <row r="2" spans="1:7" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="41" t="s">
         <v>437</v>
       </c>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>67</v>
       </c>
@@ -5587,7 +5677,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>72</v>
       </c>
@@ -5608,7 +5698,7 @@
       </c>
       <c r="G4" s="14"/>
     </row>
-    <row r="5" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>74</v>
       </c>
@@ -5627,7 +5717,7 @@
       </c>
       <c r="G5" s="14"/>
     </row>
-    <row r="6" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
         <v>75</v>
@@ -5644,7 +5734,7 @@
       </c>
       <c r="G6" s="14"/>
     </row>
-    <row r="7" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>168</v>
@@ -5661,7 +5751,7 @@
       </c>
       <c r="G7" s="14"/>
     </row>
-    <row r="8" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
         <v>169</v>
@@ -5678,7 +5768,7 @@
       </c>
       <c r="G8" s="14"/>
     </row>
-    <row r="9" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
         <v>119</v>
@@ -5695,7 +5785,7 @@
       </c>
       <c r="G9" s="14"/>
     </row>
-    <row r="10" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
         <v>103</v>
@@ -5714,7 +5804,7 @@
       </c>
       <c r="G10" s="31"/>
     </row>
-    <row r="11" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>94</v>
       </c>
@@ -5747,44 +5837,44 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:G9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.85546875" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="1" max="1" width="31.875" customWidth="1"/>
+    <col min="2" max="2" width="21.875" customWidth="1"/>
     <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" customWidth="1"/>
-    <col min="6" max="6" width="64.85546875" customWidth="1"/>
-    <col min="7" max="7" width="34.28515625" customWidth="1"/>
+    <col min="4" max="4" width="21.875" customWidth="1"/>
+    <col min="5" max="5" width="11.875" customWidth="1"/>
+    <col min="6" max="6" width="64.875" customWidth="1"/>
+    <col min="7" max="7" width="34.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="36" t="s">
         <v>307</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-    </row>
-    <row r="2" spans="1:7" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+    </row>
+    <row r="2" spans="1:7" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="41" t="s">
         <v>446</v>
       </c>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>67</v>
       </c>
@@ -5807,7 +5897,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>72</v>
       </c>
@@ -5828,7 +5918,7 @@
       </c>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>94</v>
       </c>
@@ -5849,7 +5939,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>94</v>
       </c>
@@ -5870,7 +5960,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>173</v>
@@ -5889,7 +5979,7 @@
       </c>
       <c r="G7" s="4"/>
     </row>
-    <row r="8" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
         <v>174</v>
@@ -5908,7 +5998,7 @@
       </c>
       <c r="G8" s="4"/>
     </row>
-    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
         <v>175</v>
@@ -5939,44 +6029,44 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="1" max="1" width="24.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.875" customWidth="1"/>
     <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.875" customWidth="1"/>
+    <col min="5" max="5" width="13.375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="67" customWidth="1"/>
-    <col min="7" max="7" width="32.28515625" customWidth="1"/>
+    <col min="7" max="7" width="32.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="36" t="s">
         <v>308</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-    </row>
-    <row r="2" spans="1:7" s="5" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+    </row>
+    <row r="2" spans="1:7" s="5" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="41" t="s">
         <v>447</v>
       </c>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>67</v>
       </c>
@@ -5999,7 +6089,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>72</v>
       </c>
@@ -6020,7 +6110,7 @@
       </c>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>74</v>
       </c>
@@ -6039,7 +6129,7 @@
       </c>
       <c r="G5" s="4"/>
     </row>
-    <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
         <v>75</v>
@@ -6056,7 +6146,7 @@
       </c>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>103</v>
@@ -6087,44 +6177,44 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.85546875" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="1" max="1" width="31.875" customWidth="1"/>
+    <col min="2" max="2" width="21.875" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" customWidth="1"/>
-    <col min="5" max="5" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="73.28515625" customWidth="1"/>
-    <col min="7" max="7" width="54.85546875" customWidth="1"/>
+    <col min="4" max="4" width="21.875" customWidth="1"/>
+    <col min="5" max="5" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="73.25" customWidth="1"/>
+    <col min="7" max="7" width="54.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="36" t="s">
         <v>309</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-    </row>
-    <row r="2" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+    </row>
+    <row r="2" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="40" t="s">
         <v>452</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>67</v>
       </c>
@@ -6147,7 +6237,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>72</v>
       </c>
@@ -6168,7 +6258,7 @@
       </c>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>185</v>
       </c>
@@ -6189,7 +6279,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>94</v>
       </c>
@@ -6210,7 +6300,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>179</v>
@@ -6227,7 +6317,7 @@
       </c>
       <c r="G7" s="4"/>
     </row>
-    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
         <v>180</v>
@@ -6244,7 +6334,7 @@
       </c>
       <c r="G8" s="4"/>
     </row>
-    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
         <v>182</v>
@@ -6261,7 +6351,7 @@
       </c>
       <c r="G9" s="4"/>
     </row>
-    <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
         <v>183</v>
@@ -6278,7 +6368,7 @@
       </c>
       <c r="G10" s="4"/>
     </row>
-    <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
         <v>184</v>
@@ -6309,44 +6399,44 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.85546875" customWidth="1"/>
-    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.875" customWidth="1"/>
+    <col min="2" max="2" width="30.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" customWidth="1"/>
-    <col min="5" max="5" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="64.28515625" customWidth="1"/>
-    <col min="7" max="7" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.875" customWidth="1"/>
+    <col min="5" max="5" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="64.25" customWidth="1"/>
+    <col min="7" max="7" width="17.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="36" t="s">
         <v>310</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-    </row>
-    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="40" t="s">
         <v>461</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>67</v>
       </c>
@@ -6369,7 +6459,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>72</v>
       </c>
@@ -6390,7 +6480,7 @@
       </c>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>185</v>
       </c>
@@ -6411,7 +6501,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
         <v>188</v>
@@ -6428,7 +6518,7 @@
       </c>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>189</v>
@@ -6445,7 +6535,7 @@
       </c>
       <c r="G7" s="4"/>
     </row>
-    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
         <v>190</v>
@@ -6462,7 +6552,7 @@
       </c>
       <c r="G8" s="4"/>
     </row>
-    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
         <v>191</v>
@@ -6479,7 +6569,7 @@
       </c>
       <c r="G9" s="4"/>
     </row>
-    <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
         <v>192</v>
@@ -6496,7 +6586,7 @@
       </c>
       <c r="G10" s="4"/>
     </row>
-    <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
         <v>193</v>
@@ -6513,7 +6603,7 @@
       </c>
       <c r="G11" s="4"/>
     </row>
-    <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
       <c r="B12" s="4" t="s">
         <v>194</v>
@@ -6530,7 +6620,7 @@
       </c>
       <c r="G12" s="4"/>
     </row>
-    <row r="13" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>94</v>
       </c>
@@ -6551,7 +6641,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="51" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4"/>
       <c r="B14" s="4" t="s">
         <v>196</v>
@@ -6582,44 +6672,44 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="1" max="1" width="24.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.875" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" customWidth="1"/>
+    <col min="4" max="4" width="21.875" customWidth="1"/>
+    <col min="5" max="5" width="11.875" customWidth="1"/>
     <col min="6" max="6" width="61" customWidth="1"/>
-    <col min="7" max="7" width="32.7109375" customWidth="1"/>
+    <col min="7" max="7" width="32.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="36" t="s">
         <v>311</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-    </row>
-    <row r="2" spans="1:7" ht="75.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+    </row>
+    <row r="2" spans="1:7" ht="75.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="41" t="s">
         <v>473</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>67</v>
       </c>
@@ -6642,7 +6732,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>72</v>
       </c>
@@ -6663,7 +6753,7 @@
       </c>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>94</v>
       </c>
@@ -6684,7 +6774,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
         <v>125</v>
@@ -6701,7 +6791,7 @@
       </c>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>77</v>
@@ -6718,7 +6808,7 @@
       </c>
       <c r="G7" s="4"/>
     </row>
-    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>94</v>
       </c>
@@ -6739,7 +6829,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
         <v>198</v>
@@ -6756,7 +6846,7 @@
       </c>
       <c r="G9" s="4"/>
     </row>
-    <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
         <v>199</v>
@@ -6773,7 +6863,7 @@
       </c>
       <c r="G10" s="4"/>
     </row>
-    <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
         <v>200</v>
@@ -6790,7 +6880,7 @@
       </c>
       <c r="G11" s="4"/>
     </row>
-    <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
       <c r="B12" s="4" t="s">
         <v>201</v>
@@ -6807,7 +6897,7 @@
       </c>
       <c r="G12" s="4"/>
     </row>
-    <row r="13" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>94</v>
       </c>
@@ -6828,7 +6918,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="4"/>
       <c r="B14" s="4" t="s">
         <v>79</v>
@@ -6858,45 +6948,45 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
-  <dimension ref="A1:G14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="1" max="1" width="24.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.875" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" customWidth="1"/>
-    <col min="5" max="5" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.875" customWidth="1"/>
+    <col min="5" max="5" width="17.625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="73" customWidth="1"/>
-    <col min="7" max="7" width="34.85546875" customWidth="1"/>
+    <col min="7" max="7" width="34.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="36" t="s">
         <v>312</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-    </row>
-    <row r="2" spans="1:7" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+    </row>
+    <row r="2" spans="1:7" ht="67.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="41" t="s">
         <v>473</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>67</v>
       </c>
@@ -6919,12 +7009,12 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>72</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>197</v>
+        <v>570</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>123</v>
@@ -6933,19 +7023,19 @@
         <v>107</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>71</v>
+        <v>571</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>474</v>
+        <v>572</v>
       </c>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>94</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>122</v>
+        <v>197</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>132</v>
@@ -6955,88 +7045,92 @@
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="7" t="s">
-        <v>475</v>
+        <v>573</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4"/>
+        <v>203</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>94</v>
+      </c>
       <c r="B6" s="4" t="s">
-        <v>125</v>
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>126</v>
+        <v>93</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>107</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="7" t="s">
-        <v>476</v>
-      </c>
-      <c r="G6" s="4"/>
-    </row>
-    <row r="7" spans="1:7" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>574</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
-        <v>77</v>
+        <v>575</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>138</v>
+        <v>104</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="7" t="s">
-        <v>477</v>
+        <v>576</v>
       </c>
       <c r="G7" s="4"/>
     </row>
-    <row r="8" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>94</v>
-      </c>
+    <row r="8" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="E8" s="17"/>
+      <c r="E8" s="4">
+        <v>1</v>
+      </c>
       <c r="F8" s="7" t="s">
-        <v>478</v>
-      </c>
-      <c r="G8" s="13" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>577</v>
+      </c>
+      <c r="G8" s="4"/>
+    </row>
+    <row r="9" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
-        <v>198</v>
+        <v>97</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="E9" s="4"/>
+      <c r="E9" s="4" t="s">
+        <v>83</v>
+      </c>
       <c r="F9" s="7" t="s">
-        <v>479</v>
+        <v>578</v>
       </c>
       <c r="G9" s="4"/>
     </row>
-    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>82</v>
@@ -7046,83 +7140,9 @@
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="7" t="s">
-        <v>480</v>
+        <v>579</v>
       </c>
       <c r="G10" s="4"/>
-    </row>
-    <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="7" t="s">
-        <v>481</v>
-      </c>
-      <c r="G11" s="4"/>
-    </row>
-    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="E12" s="4"/>
-      <c r="F12" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="G12" s="4"/>
-    </row>
-    <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="7" t="s">
-        <v>483</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="E14" s="4">
-        <v>1</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>484</v>
-      </c>
-      <c r="G14" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -7136,44 +7156,44 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <dimension ref="A1:G13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="1" max="1" width="24.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.875" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" customWidth="1"/>
-    <col min="5" max="5" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="54.7109375" customWidth="1"/>
-    <col min="7" max="7" width="33.7109375" customWidth="1"/>
+    <col min="4" max="4" width="21.875" customWidth="1"/>
+    <col min="5" max="5" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="54.75" customWidth="1"/>
+    <col min="7" max="7" width="33.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="36" t="s">
         <v>313</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-    </row>
-    <row r="2" spans="1:7" ht="70.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+    </row>
+    <row r="2" spans="1:7" ht="70.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="41" t="s">
         <v>485</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>67</v>
       </c>
@@ -7196,7 +7216,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>72</v>
       </c>
@@ -7217,7 +7237,7 @@
       </c>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>94</v>
       </c>
@@ -7238,7 +7258,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>94</v>
       </c>
@@ -7259,7 +7279,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>94</v>
       </c>
@@ -7280,7 +7300,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
         <v>205</v>
@@ -7297,7 +7317,7 @@
       </c>
       <c r="G8" s="4"/>
     </row>
-    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
         <v>125</v>
@@ -7314,7 +7334,7 @@
       </c>
       <c r="G9" s="4"/>
     </row>
-    <row r="10" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
         <v>206</v>
@@ -7331,7 +7351,7 @@
       </c>
       <c r="G10" s="4"/>
     </row>
-    <row r="11" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
         <v>207</v>
@@ -7350,7 +7370,7 @@
       </c>
       <c r="G11" s="4"/>
     </row>
-    <row r="12" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
       <c r="B12" s="4" t="s">
         <v>208</v>
@@ -7369,7 +7389,7 @@
       </c>
       <c r="G12" s="4"/>
     </row>
-    <row r="13" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A13" s="4"/>
       <c r="B13" s="4" t="s">
         <v>209</v>
@@ -7400,44 +7420,44 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
   <dimension ref="A1:G13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="1" max="1" width="24.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.875" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" customWidth="1"/>
-    <col min="6" max="6" width="61.140625" customWidth="1"/>
-    <col min="7" max="7" width="27.7109375" customWidth="1"/>
+    <col min="4" max="4" width="21.875" customWidth="1"/>
+    <col min="5" max="5" width="11.875" customWidth="1"/>
+    <col min="6" max="6" width="61.125" customWidth="1"/>
+    <col min="7" max="7" width="27.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-    </row>
-    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="41" t="s">
         <v>550</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>67</v>
       </c>
@@ -7460,7 +7480,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>72</v>
       </c>
@@ -7481,7 +7501,7 @@
       </c>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>74</v>
       </c>
@@ -7500,7 +7520,7 @@
       </c>
       <c r="G5" s="4"/>
     </row>
-    <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
         <v>75</v>
@@ -7517,7 +7537,7 @@
       </c>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>77</v>
@@ -7534,7 +7554,7 @@
       </c>
       <c r="G7" s="4"/>
     </row>
-    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
         <v>211</v>
@@ -7551,7 +7571,7 @@
       </c>
       <c r="G8" s="4"/>
     </row>
-    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
         <v>199</v>
@@ -7568,7 +7588,7 @@
       </c>
       <c r="G9" s="4"/>
     </row>
-    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
         <v>213</v>
@@ -7585,7 +7605,7 @@
       </c>
       <c r="G10" s="4"/>
     </row>
-    <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
         <v>214</v>
@@ -7602,7 +7622,7 @@
       </c>
       <c r="G11" s="4"/>
     </row>
-    <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>94</v>
       </c>
@@ -7623,7 +7643,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="4"/>
       <c r="B13" s="4" t="s">
         <v>79</v>
@@ -7654,44 +7674,44 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2E249CC-96A9-453B-A220-CF5C95E181D3}">
   <dimension ref="A1:G9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="57.42578125" customWidth="1"/>
-    <col min="7" max="7" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="57.375" customWidth="1"/>
+    <col min="7" max="7" width="17.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-    </row>
-    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="37" t="s">
         <v>241</v>
       </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="36"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="39"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>67</v>
       </c>
@@ -7714,7 +7734,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>72</v>
       </c>
@@ -7735,7 +7755,7 @@
       </c>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>74</v>
       </c>
@@ -7756,7 +7776,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
         <v>75</v>
@@ -7773,7 +7793,7 @@
       </c>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>77</v>
@@ -7790,7 +7810,7 @@
       </c>
       <c r="G7" s="4"/>
     </row>
-    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>94</v>
       </c>
@@ -7813,7 +7833,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
         <v>81</v>
@@ -7844,44 +7864,44 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="1" max="1" width="24.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.875" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" customWidth="1"/>
-    <col min="5" max="5" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.875" customWidth="1"/>
+    <col min="5" max="5" width="17.625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="66" customWidth="1"/>
     <col min="7" max="7" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="36" t="s">
         <v>314</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-    </row>
-    <row r="2" spans="1:7" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+    </row>
+    <row r="2" spans="1:7" ht="66.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="41" t="s">
         <v>506</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>67</v>
       </c>
@@ -7904,7 +7924,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>72</v>
       </c>
@@ -7925,7 +7945,7 @@
       </c>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>94</v>
       </c>
@@ -7946,7 +7966,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>94</v>
       </c>
@@ -7967,7 +7987,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>217</v>
@@ -7998,44 +8018,44 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1D00-000000000000}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="1" max="1" width="24.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.875" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" customWidth="1"/>
-    <col min="5" max="5" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="69.140625" customWidth="1"/>
-    <col min="7" max="7" width="29.85546875" customWidth="1"/>
+    <col min="4" max="4" width="21.875" customWidth="1"/>
+    <col min="5" max="5" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="69.125" customWidth="1"/>
+    <col min="7" max="7" width="29.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="36" t="s">
         <v>315</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-    </row>
-    <row r="2" spans="1:7" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+    </row>
+    <row r="2" spans="1:7" ht="51.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="41" t="s">
         <v>565</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>67</v>
       </c>
@@ -8058,7 +8078,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>72</v>
       </c>
@@ -8079,7 +8099,7 @@
       </c>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>94</v>
       </c>
@@ -8100,7 +8120,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>94</v>
       </c>
@@ -8121,7 +8141,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>220</v>
@@ -8138,7 +8158,7 @@
       </c>
       <c r="G7" s="4"/>
     </row>
-    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
         <v>221</v>
@@ -8155,7 +8175,7 @@
       </c>
       <c r="G8" s="4"/>
     </row>
-    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
         <v>79</v>
@@ -8174,7 +8194,7 @@
       </c>
       <c r="G9" s="4"/>
     </row>
-    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
         <v>199</v>
@@ -8193,7 +8213,7 @@
       </c>
       <c r="G10" s="4"/>
     </row>
-    <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
         <v>202</v>
@@ -8223,44 +8243,44 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA7E44C4-E4B6-4DCC-BE19-C7DF38E6CEDD}">
   <dimension ref="A1:G10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="24" customWidth="1"/>
     <col min="6" max="6" width="65" customWidth="1"/>
-    <col min="7" max="7" width="35.85546875" customWidth="1"/>
+    <col min="7" max="7" width="35.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="36" t="s">
         <v>551</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-    </row>
-    <row r="2" spans="1:7" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+    </row>
+    <row r="2" spans="1:7" ht="63.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="41" t="s">
         <v>556</v>
       </c>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>67</v>
       </c>
@@ -8283,7 +8303,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>72</v>
       </c>
@@ -8304,7 +8324,7 @@
       </c>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>94</v>
       </c>
@@ -8325,7 +8345,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>94</v>
       </c>
@@ -8346,7 +8366,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="9" t="s">
         <v>336</v>
@@ -8363,7 +8383,7 @@
       </c>
       <c r="G7" s="7"/>
     </row>
-    <row r="8" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="50.4" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
       <c r="B8" s="9" t="s">
         <v>79</v>
@@ -8382,7 +8402,7 @@
       </c>
       <c r="G8" s="7"/>
     </row>
-    <row r="9" spans="1:7" ht="49.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
       <c r="B9" s="9" t="s">
         <v>199</v>
@@ -8401,7 +8421,7 @@
       </c>
       <c r="G9" s="7"/>
     </row>
-    <row r="10" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="67.2" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
       <c r="B10" s="9" t="s">
         <v>202</v>
@@ -8431,44 +8451,44 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1E00-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.85546875" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="1" max="1" width="31.875" customWidth="1"/>
+    <col min="2" max="2" width="21.875" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" customWidth="1"/>
-    <col min="5" max="5" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="61.5703125" customWidth="1"/>
-    <col min="7" max="7" width="35.140625" customWidth="1"/>
+    <col min="4" max="4" width="21.875" customWidth="1"/>
+    <col min="5" max="5" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="61.625" customWidth="1"/>
+    <col min="7" max="7" width="35.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="36" t="s">
         <v>316</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-    </row>
-    <row r="2" spans="1:7" ht="71.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+    </row>
+    <row r="2" spans="1:7" ht="71.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="41" t="s">
         <v>520</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>67</v>
       </c>
@@ -8491,7 +8511,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>72</v>
       </c>
@@ -8512,7 +8532,7 @@
       </c>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>94</v>
       </c>
@@ -8533,7 +8553,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>94</v>
       </c>
@@ -8554,7 +8574,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>224</v>
@@ -8571,7 +8591,7 @@
       </c>
       <c r="G7" s="4"/>
     </row>
-    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
         <v>225</v>
@@ -8588,7 +8608,7 @@
       </c>
       <c r="G8" s="4"/>
     </row>
-    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
         <v>226</v>
@@ -8605,7 +8625,7 @@
       </c>
       <c r="G9" s="4"/>
     </row>
-    <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
         <v>141</v>
@@ -8622,7 +8642,7 @@
       </c>
       <c r="G10" s="4"/>
     </row>
-    <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
         <v>143</v>
@@ -8639,7 +8659,7 @@
       </c>
       <c r="G11" s="4"/>
     </row>
-    <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>94</v>
       </c>
@@ -8660,7 +8680,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4"/>
       <c r="B13" s="4" t="s">
         <v>145</v>
@@ -8679,7 +8699,7 @@
       </c>
       <c r="G13" s="4"/>
     </row>
-    <row r="14" spans="1:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="67.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4"/>
       <c r="B14" s="4" t="s">
         <v>227</v>
@@ -8710,44 +8730,44 @@
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1F00-000000000000}">
   <dimension ref="A1:G13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.85546875" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="1" max="1" width="31.875" customWidth="1"/>
+    <col min="2" max="2" width="21.875" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" customWidth="1"/>
-    <col min="6" max="6" width="54.28515625" customWidth="1"/>
-    <col min="7" max="7" width="40.42578125" customWidth="1"/>
+    <col min="4" max="4" width="21.875" customWidth="1"/>
+    <col min="5" max="5" width="11.875" customWidth="1"/>
+    <col min="6" max="6" width="54.25" customWidth="1"/>
+    <col min="7" max="7" width="40.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="36" t="s">
         <v>317</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-    </row>
-    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="41" t="s">
         <v>532</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>67</v>
       </c>
@@ -8770,7 +8790,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>72</v>
       </c>
@@ -8791,7 +8811,7 @@
       </c>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>94</v>
       </c>
@@ -8812,7 +8832,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>94</v>
       </c>
@@ -8833,7 +8853,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>125</v>
@@ -8850,7 +8870,7 @@
       </c>
       <c r="G7" s="4"/>
     </row>
-    <row r="8" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
         <v>77</v>
@@ -8867,7 +8887,7 @@
       </c>
       <c r="G8" s="4"/>
     </row>
-    <row r="9" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
         <v>229</v>
@@ -8884,7 +8904,7 @@
       </c>
       <c r="G9" s="4"/>
     </row>
-    <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
         <v>199</v>
@@ -8901,7 +8921,7 @@
       </c>
       <c r="G10" s="4"/>
     </row>
-    <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
         <v>202</v>
@@ -8918,7 +8938,7 @@
       </c>
       <c r="G11" s="4"/>
     </row>
-    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>94</v>
       </c>
@@ -8939,7 +8959,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="4"/>
       <c r="B13" s="4" t="s">
         <v>230</v>
@@ -8970,44 +8990,44 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2000-000000000000}">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.85546875" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="1" max="1" width="31.875" customWidth="1"/>
+    <col min="2" max="2" width="21.875" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" customWidth="1"/>
-    <col min="6" max="6" width="63.28515625" customWidth="1"/>
-    <col min="7" max="7" width="54.85546875" customWidth="1"/>
+    <col min="4" max="4" width="21.875" customWidth="1"/>
+    <col min="5" max="5" width="11.875" customWidth="1"/>
+    <col min="6" max="6" width="63.25" customWidth="1"/>
+    <col min="7" max="7" width="54.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="36" t="s">
         <v>319</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-    </row>
-    <row r="2" spans="1:7" ht="70.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+    </row>
+    <row r="2" spans="1:7" ht="70.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="41" t="s">
         <v>547</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>67</v>
       </c>
@@ -9030,7 +9050,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>72</v>
       </c>
@@ -9049,7 +9069,7 @@
       </c>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>94</v>
       </c>
@@ -9068,7 +9088,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>94</v>
       </c>
@@ -9087,7 +9107,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>232</v>
@@ -9116,44 +9136,44 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="17.42578125" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.85546875" customWidth="1"/>
+    <col min="2" max="2" width="17.375" customWidth="1"/>
+    <col min="3" max="3" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.875" customWidth="1"/>
     <col min="5" max="5" width="22" customWidth="1"/>
-    <col min="6" max="6" width="61.7109375" customWidth="1"/>
-    <col min="7" max="7" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="61.75" customWidth="1"/>
+    <col min="7" max="7" width="26.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-    </row>
-    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="40" t="s">
         <v>249</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>67</v>
       </c>
@@ -9176,7 +9196,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>72</v>
       </c>
@@ -9197,7 +9217,7 @@
       </c>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="4" t="s">
         <v>85</v>
@@ -9214,7 +9234,7 @@
       </c>
       <c r="G5" s="4"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
         <v>86</v>
@@ -9231,7 +9251,7 @@
       </c>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>87</v>
@@ -9248,7 +9268,7 @@
       </c>
       <c r="G7" s="4"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>74</v>
       </c>
@@ -9267,7 +9287,7 @@
       </c>
       <c r="G8" s="4"/>
     </row>
-    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
         <v>90</v>
@@ -9284,7 +9304,7 @@
       </c>
       <c r="G9" s="4"/>
     </row>
-    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
         <v>79</v>
@@ -9303,7 +9323,7 @@
       </c>
       <c r="G10" s="4"/>
     </row>
-    <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
         <v>81</v>
@@ -9333,45 +9353,45 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.85546875" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="1" max="1" width="31.875" customWidth="1"/>
+    <col min="2" max="2" width="21.875" customWidth="1"/>
     <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" customWidth="1"/>
-    <col min="5" max="5" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="67.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.875" customWidth="1"/>
+    <col min="5" max="5" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="67.75" customWidth="1"/>
+    <col min="7" max="7" width="15.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-    </row>
-    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="40" t="s">
         <v>254</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>67</v>
       </c>
@@ -9394,7 +9414,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>72</v>
       </c>
@@ -9415,7 +9435,7 @@
       </c>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>94</v>
       </c>
@@ -9436,7 +9456,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>94</v>
       </c>
@@ -9457,7 +9477,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>79</v>
@@ -9476,7 +9496,7 @@
       </c>
       <c r="G7" s="4"/>
     </row>
-    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
         <v>97</v>
@@ -9494,6 +9514,25 @@
         <v>253</v>
       </c>
       <c r="G8" s="4"/>
+    </row>
+    <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="G9" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -9507,44 +9546,44 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.85546875" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="1" max="1" width="31.875" customWidth="1"/>
+    <col min="2" max="2" width="21.875" customWidth="1"/>
     <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" customWidth="1"/>
-    <col min="5" max="5" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.85546875" customWidth="1"/>
-    <col min="7" max="7" width="36.140625" customWidth="1"/>
+    <col min="4" max="4" width="21.875" customWidth="1"/>
+    <col min="5" max="5" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.875" customWidth="1"/>
+    <col min="7" max="7" width="36.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-    </row>
-    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="40" t="s">
         <v>255</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>67</v>
       </c>
@@ -9567,7 +9606,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>72</v>
       </c>
@@ -9588,7 +9627,7 @@
       </c>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>94</v>
       </c>
@@ -9609,7 +9648,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>74</v>
       </c>
@@ -9628,7 +9667,7 @@
       </c>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="9" t="s">
         <v>75</v>
@@ -9645,7 +9684,7 @@
       </c>
       <c r="G7" s="4"/>
     </row>
-    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="9" t="s">
         <v>263</v>
@@ -9662,7 +9701,7 @@
       </c>
       <c r="G8" s="4"/>
     </row>
-    <row r="9" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="9" t="s">
         <v>264</v>
@@ -9679,7 +9718,7 @@
       </c>
       <c r="G9" s="4"/>
     </row>
-    <row r="10" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="9" t="s">
         <v>103</v>
@@ -9698,7 +9737,7 @@
       </c>
       <c r="G10" s="4"/>
     </row>
-    <row r="11" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
         <v>81</v>
@@ -9729,44 +9768,44 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="1" max="1" width="24.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.875" customWidth="1"/>
     <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" customWidth="1"/>
-    <col min="5" max="5" width="17.5703125" style="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.28515625" customWidth="1"/>
+    <col min="4" max="4" width="21.875" customWidth="1"/>
+    <col min="5" max="5" width="17.625" style="20" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.25" customWidth="1"/>
     <col min="7" max="7" width="37" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-    </row>
-    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="40" t="s">
         <v>266</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>67</v>
       </c>
@@ -9789,7 +9828,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>72</v>
       </c>
@@ -9810,7 +9849,7 @@
       </c>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>94</v>
       </c>
@@ -9831,7 +9870,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>94</v>
       </c>
@@ -9852,7 +9891,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>267</v>
@@ -9871,7 +9910,7 @@
       </c>
       <c r="G7" s="4"/>
     </row>
-    <row r="8" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
         <v>79</v>
@@ -9890,7 +9929,7 @@
       </c>
       <c r="G8" s="4"/>
     </row>
-    <row r="9" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
         <v>199</v>
@@ -9909,7 +9948,7 @@
       </c>
       <c r="G9" s="4"/>
     </row>
-    <row r="10" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
         <v>202</v>
@@ -9938,44 +9977,44 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:G9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="1" max="1" width="24.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.875" customWidth="1"/>
     <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" customWidth="1"/>
-    <col min="6" max="6" width="35.85546875" customWidth="1"/>
-    <col min="7" max="7" width="38.85546875" customWidth="1"/>
+    <col min="4" max="4" width="21.875" customWidth="1"/>
+    <col min="5" max="5" width="20.625" customWidth="1"/>
+    <col min="6" max="6" width="35.875" customWidth="1"/>
+    <col min="7" max="7" width="38.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-    </row>
-    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="40" t="s">
         <v>278</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>67</v>
       </c>
@@ -9998,7 +10037,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>72</v>
       </c>
@@ -10019,7 +10058,7 @@
       </c>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>74</v>
       </c>
@@ -10038,7 +10077,7 @@
       </c>
       <c r="G5" s="4"/>
     </row>
-    <row r="6" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
         <v>75</v>
@@ -10055,7 +10094,7 @@
       </c>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>77</v>
@@ -10072,7 +10111,7 @@
       </c>
       <c r="G7" s="4"/>
     </row>
-    <row r="8" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
         <v>79</v>
@@ -10091,7 +10130,7 @@
       </c>
       <c r="G8" s="4"/>
     </row>
-    <row r="9" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
         <v>81</v>
@@ -10120,44 +10159,44 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="1" max="1" width="24.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.875" customWidth="1"/>
     <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" customWidth="1"/>
-    <col min="5" max="5" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.85546875" customWidth="1"/>
-    <col min="7" max="7" width="38.85546875" customWidth="1"/>
+    <col min="4" max="4" width="21.875" customWidth="1"/>
+    <col min="5" max="5" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.875" customWidth="1"/>
+    <col min="7" max="7" width="38.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-    </row>
-    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="40" t="s">
         <v>279</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>67</v>
       </c>
@@ -10180,7 +10219,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>72</v>
       </c>
@@ -10201,7 +10240,7 @@
       </c>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>94</v>
       </c>
@@ -10222,7 +10261,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>94</v>
       </c>
@@ -10243,7 +10282,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>79</v>
@@ -10262,7 +10301,7 @@
       </c>
       <c r="G7" s="4"/>
     </row>
-    <row r="8" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
         <v>114</v>
